--- a/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION FINAL FASE 2.xlsx
+++ b/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION FINAL FASE 2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://duoccl0-my.sharepoint.com/personal/ge_galan_profesor_duoc_cl/Documents/2024-2/Clases/CAPSTONE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\OneDrive\Escritorio\Capstone\Capstone_DuocUc_2025\Fase 2\Evidencias grupales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="746" documentId="8_{2EFDF332-31E9-4C74-A6B5-E695634C1C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A524BC42-4BE6-4992-8E50-65D453B1EC65}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B5855F-1421-41DA-AD0B-9487FDC92110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
   <si>
     <t>PUNTOS</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>No generan evidencias dentro del repositorio  del proyecto del aporte de cada uno de los integrantes del equipo por lo que no se permite identificar la equidad en el trabajo y la participación de cada estudiante</t>
+  </si>
+  <si>
+    <t>Victor Gamboa Blanco</t>
   </si>
 </sst>
 </file>
@@ -932,50 +935,6 @@
     <xf numFmtId="9" fontId="14" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
@@ -1003,6 +962,50 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1341,25 +1344,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42" t="s">
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43" t="s">
+      <c r="A2" s="51"/>
+      <c r="B2" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="52" t="s">
         <v>21</v>
       </c>
       <c r="D2" s="36" t="s">
@@ -1368,19 +1371,19 @@
       <c r="E2" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="42"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="42"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="43"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
       <c r="D3" s="37">
         <v>-0.3</v>
       </c>
       <c r="E3" s="37">
         <v>0</v>
       </c>
-      <c r="F3" s="42"/>
+      <c r="F3" s="51"/>
     </row>
     <row r="4" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A4" s="38" t="s">
@@ -1403,7 +1406,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="42" t="s">
         <v>44</v>
       </c>
       <c r="B5" s="38" t="s">
@@ -1423,7 +1426,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="42" t="s">
         <v>49</v>
       </c>
       <c r="B6" s="38" t="s">
@@ -1443,19 +1446,19 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="69" x14ac:dyDescent="0.3">
-      <c r="A7" s="65" t="s">
+      <c r="A7" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="66" t="s">
+      <c r="C7" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="D7" s="66" t="s">
+      <c r="D7" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="67" t="s">
+      <c r="E7" s="45" t="s">
         <v>58</v>
       </c>
       <c r="F7" s="39">
@@ -1463,7 +1466,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="42" t="s">
         <v>59</v>
       </c>
       <c r="B8" s="38" t="s">
@@ -1483,7 +1486,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="42" t="s">
         <v>35</v>
       </c>
       <c r="B9" s="38" t="s">
@@ -1503,7 +1506,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="42" t="s">
         <v>64</v>
       </c>
       <c r="B10" s="38" t="s">
@@ -1523,7 +1526,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="68" t="s">
+      <c r="A11" s="46" t="s">
         <v>69</v>
       </c>
       <c r="B11" s="27" t="s">
@@ -1535,7 +1538,7 @@
       <c r="D11" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="E11" s="69" t="s">
+      <c r="E11" s="47" t="s">
         <v>38</v>
       </c>
       <c r="F11" s="39">
@@ -1543,22 +1546,22 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="71" t="s">
+      <c r="C12" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="49" t="s">
         <v>74</v>
       </c>
-      <c r="E12" s="71" t="s">
+      <c r="E12" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="F12" s="72">
+      <c r="F12" s="50">
         <v>15</v>
       </c>
     </row>
@@ -1619,7 +1622,7 @@
       <c r="D2" s="2">
         <v>0.25</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="68">
         <v>1</v>
       </c>
     </row>
@@ -1633,7 +1636,7 @@
       <c r="D3" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="45"/>
+      <c r="E3" s="54"/>
     </row>
     <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
@@ -1655,87 +1658,57 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4">
-        <v>2</v>
-      </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="5">
-        <f>EVALUACION1!$C$21</f>
-        <v>7</v>
-      </c>
-      <c r="D5" s="5">
-        <f>C44</f>
-        <v>7</v>
-      </c>
-      <c r="E5" s="6">
-        <f t="shared" ref="E5:E6" si="0">C5*C$2+D5*D$2</f>
-        <v>7</v>
-      </c>
-      <c r="G5" s="1"/>
+      <c r="A5" s="4"/>
+      <c r="C5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>3</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="5">
-        <f>EVALUACION1!$C$21</f>
-        <v>7</v>
-      </c>
-      <c r="D6" s="5">
-        <f>C55</f>
-        <v>7</v>
-      </c>
-      <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G6" s="1"/>
+      <c r="A6" s="4"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="18" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="60" t="s">
+      <c r="A11" s="69" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="15"/>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="54"/>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="64"/>
     </row>
     <row r="12" spans="1:11" ht="14.4" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="56"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="45"/>
-      <c r="D12" s="53" t="s">
+      <c r="C12" s="54"/>
+      <c r="D12" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="54"/>
-      <c r="F12" s="53" t="s">
+      <c r="E12" s="64"/>
+      <c r="F12" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="54"/>
-      <c r="H12" s="57" t="s">
+      <c r="G12" s="64"/>
+      <c r="H12" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="54"/>
-      <c r="J12" s="53" t="s">
+      <c r="I12" s="64"/>
+      <c r="J12" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="54"/>
+      <c r="K12" s="64"/>
     </row>
     <row r="13" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="61"/>
+      <c r="A13" s="70"/>
       <c r="B13" s="31" t="str">
         <f>RUBRICA!A4</f>
         <v>1. Implementa una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</v>
@@ -1744,7 +1717,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="17" t="str">
-        <f t="shared" ref="D13:D16" si="1">IF($C13=CL,"X","")</f>
+        <f t="shared" ref="D13:D16" si="0">IF($C13=CL,"X","")</f>
         <v>X</v>
       </c>
       <c r="E13" s="17">
@@ -1752,7 +1725,7 @@
         <v>10</v>
       </c>
       <c r="F13" s="17" t="str">
-        <f t="shared" ref="F13:F16" si="2">IF($C13=L,"X","")</f>
+        <f t="shared" ref="F13:F16" si="1">IF($C13=L,"X","")</f>
         <v/>
       </c>
       <c r="G13" s="17" t="str">
@@ -1760,7 +1733,7 @@
         <v/>
       </c>
       <c r="H13" s="17" t="str">
-        <f t="shared" ref="H13:H16" si="3">IF($C13=ML,"X","")</f>
+        <f t="shared" ref="H13:H16" si="2">IF($C13=ML,"X","")</f>
         <v/>
       </c>
       <c r="I13" s="17" t="str">
@@ -1768,16 +1741,16 @@
         <v/>
       </c>
       <c r="J13" s="17" t="str">
-        <f t="shared" ref="J13:J16" si="4">IF($C13=NL,"X","")</f>
+        <f t="shared" ref="J13:J16" si="3">IF($C13=NL,"X","")</f>
         <v/>
       </c>
       <c r="K13" s="17" t="str">
-        <f t="shared" ref="K13:K16" si="5">IF($J13="X",0,"")</f>
+        <f t="shared" ref="K13:K16" si="4">IF($J13="X",0,"")</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:11" ht="36" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="61"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="31" t="str">
         <f>RUBRICA!A5</f>
         <v>2. Genera evidencias que dan cuenta del cumplimiento del Proyecto CAPSTONE, en relación a documentación, programación y almacenamiento de datos, de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria</v>
@@ -1786,7 +1759,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>X</v>
       </c>
       <c r="E14" s="17">
@@ -1794,7 +1767,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G14" s="17" t="str">
@@ -1802,7 +1775,7 @@
         <v/>
       </c>
       <c r="H14" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I14" s="17" t="str">
@@ -1810,16 +1783,16 @@
         <v/>
       </c>
       <c r="J14" s="17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K14" s="17" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K14" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="61"/>
+    </row>
+    <row r="15" spans="1:11" ht="14.4" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="70"/>
       <c r="B15" s="31" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Relaciona el Proyecto APT con las competencias del perfil de egreso de su Plan de Estudio.</v>
@@ -1828,7 +1801,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>X</v>
       </c>
       <c r="E15" s="17">
@@ -1836,7 +1809,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G15" s="17" t="str">
@@ -1844,7 +1817,7 @@
         <v/>
       </c>
       <c r="H15" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I15" s="17" t="str">
@@ -1852,16 +1825,16 @@
         <v/>
       </c>
       <c r="J15" s="17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K15" s="17" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K15" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
     </row>
     <row r="16" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="61"/>
+      <c r="A16" s="70"/>
       <c r="B16" s="31" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</v>
@@ -1870,7 +1843,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>X</v>
       </c>
       <c r="E16" s="17">
@@ -1878,7 +1851,7 @@
         <v>5</v>
       </c>
       <c r="F16" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G16" s="17" t="str">
@@ -1886,7 +1859,7 @@
         <v/>
       </c>
       <c r="H16" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="I16" s="17" t="str">
@@ -1894,16 +1867,16 @@
         <v/>
       </c>
       <c r="J16" s="17" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="K16" s="17" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
-      <c r="K16" s="17" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
     </row>
     <row r="17" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="61"/>
+      <c r="A17" s="70"/>
       <c r="B17" s="31" t="str">
         <f>RUBRICA!A9</f>
         <v xml:space="preserve">6. Utiliza correctamente las reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
@@ -1940,12 +1913,12 @@
         <v/>
       </c>
       <c r="K17" s="17" t="str">
-        <f t="shared" ref="K17:K19" si="6">IF($J17="X",0,"")</f>
+        <f t="shared" ref="K17:K19" si="5">IF($J17="X",0,"")</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="61"/>
+      <c r="A18" s="70"/>
       <c r="B18" s="31" t="str">
         <f>RUBRICA!A10</f>
         <v>7. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estrucutra y nombres solicitados, guardando todas las evidencias de avances en Git</v>
@@ -1982,12 +1955,12 @@
         <v/>
       </c>
       <c r="K18" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.8" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="61"/>
+      <c r="A19" s="70"/>
       <c r="B19" s="31" t="str">
         <f>RUBRICA!A12</f>
         <v>9.-Generan evidencias claras dentro del repositorio  del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</v>
@@ -2024,12 +1997,12 @@
         <v/>
       </c>
       <c r="K19" s="17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="56"/>
+      <c r="A20" s="67"/>
       <c r="B20" s="30" t="s">
         <v>4</v>
       </c>
@@ -2059,7 +2032,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="45"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="33" t="s">
         <v>13</v>
       </c>
@@ -2071,82 +2044,81 @@
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="44" t="s">
+      <c r="B24" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="47">
-        <f>$B$4</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="49"/>
+      <c r="C24" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="56"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
+      <c r="G24" s="56"/>
+      <c r="H24" s="56"/>
+      <c r="I24" s="56"/>
+      <c r="J24" s="56"/>
+      <c r="K24" s="57"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="56"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51"/>
-      <c r="F25" s="51"/>
-      <c r="G25" s="51"/>
-      <c r="H25" s="51"/>
-      <c r="I25" s="51"/>
-      <c r="J25" s="51"/>
-      <c r="K25" s="52"/>
+      <c r="A25" s="67"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="60"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="56"/>
+      <c r="A26" s="67"/>
       <c r="B26" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="53" t="s">
+      <c r="D26" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="54"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="64"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="56"/>
+      <c r="A27" s="67"/>
       <c r="B27" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="45"/>
-      <c r="D27" s="53" t="s">
+      <c r="C27" s="54"/>
+      <c r="D27" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="54"/>
-      <c r="F27" s="53" t="s">
+      <c r="E27" s="64"/>
+      <c r="F27" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="54"/>
-      <c r="H27" s="57" t="s">
+      <c r="G27" s="64"/>
+      <c r="H27" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="54"/>
-      <c r="J27" s="53" t="s">
+      <c r="I27" s="64"/>
+      <c r="J27" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="K27" s="54"/>
-    </row>
-    <row r="28" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A28" s="56"/>
+      <c r="K27" s="64"/>
+    </row>
+    <row r="28" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="67"/>
       <c r="B28" s="31" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
@@ -2155,7 +2127,7 @@
         <v>5</v>
       </c>
       <c r="D28" s="17" t="str">
-        <f t="shared" ref="D28:D30" si="7">IF($C28=CL,"X","")</f>
+        <f t="shared" ref="D28:D30" si="6">IF($C28=CL,"X","")</f>
         <v>X</v>
       </c>
       <c r="E28" s="17">
@@ -2163,7 +2135,7 @@
         <v>5</v>
       </c>
       <c r="F28" s="17" t="str">
-        <f t="shared" ref="F28:F30" si="8">IF($C28=L,"X","")</f>
+        <f t="shared" ref="F28:F30" si="7">IF($C28=L,"X","")</f>
         <v/>
       </c>
       <c r="G28" s="17" t="str">
@@ -2171,7 +2143,7 @@
         <v/>
       </c>
       <c r="H28" s="17" t="str">
-        <f t="shared" ref="H28:H30" si="9">IF($C28=ML,"X","")</f>
+        <f t="shared" ref="H28:H30" si="8">IF($C28=ML,"X","")</f>
         <v/>
       </c>
       <c r="I28" s="17" t="str">
@@ -2179,16 +2151,16 @@
         <v/>
       </c>
       <c r="J28" s="17" t="str">
-        <f t="shared" ref="J28:J30" si="10">IF($C28=NL,"X","")</f>
+        <f t="shared" ref="J28:J30" si="9">IF($C28=NL,"X","")</f>
         <v/>
       </c>
       <c r="K28" s="17" t="str">
-        <f t="shared" ref="K28:K30" si="11">IF($J28="X",0,"")</f>
+        <f t="shared" ref="K28:K30" si="10">IF($J28="X",0,"")</f>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:11" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="31" t="str">
         <f>RUBRICA!A11</f>
         <v>8. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
@@ -2197,7 +2169,7 @@
         <v>5</v>
       </c>
       <c r="D29" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>X</v>
       </c>
       <c r="E29" s="17">
@@ -2205,7 +2177,7 @@
         <v>10</v>
       </c>
       <c r="F29" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G29" s="17" t="str">
@@ -2213,7 +2185,7 @@
         <v/>
       </c>
       <c r="H29" s="17" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I29" s="17" t="str">
@@ -2221,16 +2193,16 @@
         <v/>
       </c>
       <c r="J29" s="17" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K29" s="17" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="K29" s="17" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
     </row>
     <row r="30" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="56"/>
+      <c r="A30" s="67"/>
       <c r="B30" s="31" t="str">
         <f>RUBRICA!A13</f>
         <v>10. Colaboración y trabajo en equipo *</v>
@@ -2239,7 +2211,7 @@
         <v>5</v>
       </c>
       <c r="D30" s="17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>X</v>
       </c>
       <c r="E30" s="17">
@@ -2247,7 +2219,7 @@
         <v>10</v>
       </c>
       <c r="F30" s="17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="G30" s="17" t="str">
@@ -2255,7 +2227,7 @@
         <v/>
       </c>
       <c r="H30" s="17" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="I30" s="17" t="str">
@@ -2263,16 +2235,16 @@
         <v/>
       </c>
       <c r="J30" s="17" t="str">
+        <f t="shared" si="9"/>
+        <v/>
+      </c>
+      <c r="K30" s="17" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
-      <c r="K30" s="17" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="56"/>
+      <c r="A31" s="67"/>
       <c r="B31" s="22" t="s">
         <v>14</v>
       </c>
@@ -2302,7 +2274,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="45"/>
+      <c r="A32" s="54"/>
       <c r="B32" s="18" t="s">
         <v>13</v>
       </c>
@@ -2311,517 +2283,67 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
     </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="23"/>
       <c r="C34" s="24"/>
     </row>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="55" t="s">
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="47">
-        <f>B5</f>
-        <v>0</v>
-      </c>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="49"/>
-    </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="56"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="52"/>
-    </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="56"/>
-      <c r="B38" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="58"/>
-      <c r="K38" s="54"/>
-    </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="56"/>
-      <c r="B39" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C39" s="45"/>
-      <c r="D39" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="E39" s="54"/>
-      <c r="F39" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="G39" s="54"/>
-      <c r="H39" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="I39" s="54"/>
-      <c r="J39" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="K39" s="54"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="56"/>
-      <c r="B40" s="31" t="str">
-        <f>RUBRICA!A6</f>
-        <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
-      </c>
-      <c r="C40" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D40" s="17" t="str">
-        <f t="shared" ref="D40:D42" si="12">IF($C40=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E40" s="17">
-        <f>IF(D40="X",100*0.05,"")</f>
-        <v>5</v>
-      </c>
-      <c r="F40" s="17" t="str">
-        <f t="shared" ref="F40:F42" si="13">IF($C40=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G40" s="17" t="str">
-        <f>IF(F40="X",60*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="17" t="str">
-        <f t="shared" ref="H40:H42" si="14">IF($C40=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I40" s="17" t="str">
-        <f>IF(H40="X",30*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="J40" s="17" t="str">
-        <f t="shared" ref="J40:J42" si="15">IF($C40=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K40" s="17" t="str">
-        <f t="shared" ref="K40:K42" si="16">IF($J40="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="56"/>
-      <c r="B41" s="31" t="str">
-        <f>RUBRICA!A11</f>
-        <v>8. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
-      </c>
-      <c r="C41" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="17" t="str">
-        <f t="shared" si="12"/>
-        <v>X</v>
-      </c>
-      <c r="E41" s="17">
-        <f>IF(D41="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F41" s="17" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G41" s="17" t="str">
-        <f>IF(F41="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I41" s="17" t="str">
-        <f>IF(H41="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J41" s="17" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K41" s="17" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="56"/>
-      <c r="B42" s="31" t="str">
-        <f>RUBRICA!A13</f>
-        <v>10. Colaboración y trabajo en equipo *</v>
-      </c>
-      <c r="C42" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="17" t="str">
-        <f t="shared" si="12"/>
-        <v>X</v>
-      </c>
-      <c r="E42" s="17">
-        <f>IF(D42="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F42" s="17" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="G42" s="17" t="str">
-        <f>IF(F42="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="17" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="I42" s="17" t="str">
-        <f>IF(H42="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J42" s="17" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K42" s="17" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="56"/>
-      <c r="B43" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="19">
-        <f>E43+G43+I43+K43</f>
-        <v>25</v>
-      </c>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20">
-        <f>SUM(E40:E42)</f>
-        <v>25</v>
-      </c>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20">
-        <f>SUM(G40:G42)</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20">
-        <f>SUM(I40:I42)</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20">
-        <f>SUM(K41:K42)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="45"/>
-      <c r="B44" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C44" s="21">
-        <f>VLOOKUP(C43,ESCALA_TRAB_EQUIP!A1:B52,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="23"/>
-      <c r="C45" s="24"/>
-    </row>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B46" s="23"/>
-      <c r="C46" s="24"/>
-    </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" s="47">
-        <f>B6</f>
-        <v>0</v>
-      </c>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
-      <c r="I47" s="48"/>
-      <c r="J47" s="48"/>
-      <c r="K47" s="49"/>
-    </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="56"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="51"/>
-      <c r="K48" s="52"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="56"/>
-      <c r="B49" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="53" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
-      <c r="J49" s="58"/>
-      <c r="K49" s="54"/>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="56"/>
-      <c r="B50" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="45"/>
-      <c r="D50" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="E50" s="54"/>
-      <c r="F50" s="53" t="s">
-        <v>6</v>
-      </c>
-      <c r="G50" s="54"/>
-      <c r="H50" s="57" t="s">
-        <v>27</v>
-      </c>
-      <c r="I50" s="54"/>
-      <c r="J50" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="K50" s="54"/>
-    </row>
-    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="56"/>
-      <c r="B51" s="31" t="str">
-        <f>RUBRICA!A6</f>
-        <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
-      </c>
-      <c r="C51" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D51" s="17" t="str">
-        <f t="shared" ref="D51:D53" si="17">IF($C51=CL,"X","")</f>
-        <v>X</v>
-      </c>
-      <c r="E51" s="17">
-        <f>IF(D51="X",100*0.05,"")</f>
-        <v>5</v>
-      </c>
-      <c r="F51" s="17" t="str">
-        <f t="shared" ref="F51:F53" si="18">IF($C51=L,"X","")</f>
-        <v/>
-      </c>
-      <c r="G51" s="17" t="str">
-        <f>IF(F51="X",60*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="17" t="str">
-        <f t="shared" ref="H51:H53" si="19">IF($C51=ML,"X","")</f>
-        <v/>
-      </c>
-      <c r="I51" s="17" t="str">
-        <f>IF(H51="X",30*0.05,"")</f>
-        <v/>
-      </c>
-      <c r="J51" s="17" t="str">
-        <f t="shared" ref="J51:J53" si="20">IF($C51=NL,"X","")</f>
-        <v/>
-      </c>
-      <c r="K51" s="17" t="str">
-        <f t="shared" ref="K51:K53" si="21">IF($J51="X",0,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="56"/>
-      <c r="B52" s="31" t="str">
-        <f>RUBRICA!A11</f>
-        <v>8. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
-      </c>
-      <c r="C52" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="17" t="str">
-        <f t="shared" si="17"/>
-        <v>X</v>
-      </c>
-      <c r="E52" s="17">
-        <f>IF(D52="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F52" s="17" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="G52" s="17" t="str">
-        <f>IF(F52="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="17" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I52" s="17" t="str">
-        <f>IF(H52="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="17" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K52" s="17" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="56"/>
-      <c r="B53" s="31" t="str">
-        <f>RUBRICA!A13</f>
-        <v>10. Colaboración y trabajo en equipo *</v>
-      </c>
-      <c r="C53" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D53" s="17" t="str">
-        <f t="shared" si="17"/>
-        <v>X</v>
-      </c>
-      <c r="E53" s="17">
-        <f>IF(D53="X",100*0.1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="F53" s="17" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="G53" s="17" t="str">
-        <f>IF(F53="X",60*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="17" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I53" s="17" t="str">
-        <f>IF(H53="X",30*0.1,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="17" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K53" s="17" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="56"/>
-      <c r="B54" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="19">
-        <f>E54+G54+I54+K54</f>
-        <v>25</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20">
-        <f>SUM(E51:E53)</f>
-        <v>25</v>
-      </c>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20">
-        <f>SUM(G51:G53)</f>
-        <v>0</v>
-      </c>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20">
-        <f>SUM(I51:I53)</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20">
-        <f>SUM(K52:K53)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="45"/>
-      <c r="B55" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="21">
-        <f>VLOOKUP(C54,ESCALA_TRAB_EQUIP!A1:B52,2,FALSE)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="67"/>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="67"/>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="67"/>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="67"/>
+    </row>
+    <row r="52" spans="1:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="67"/>
+    </row>
+    <row r="53" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="67"/>
+    </row>
+    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="67"/>
+    </row>
+    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="54"/>
+    </row>
+    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="23"/>
       <c r="C56" s="24"/>
     </row>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3685,16 +3207,10 @@
     <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:K37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="D38:K38"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="A36:A44"/>
+  <mergeCells count="18">
+    <mergeCell ref="A47:A55"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="J27:K27"/>
     <mergeCell ref="A24:A32"/>
     <mergeCell ref="E2:E3"/>
     <mergeCell ref="C11:C12"/>
@@ -3710,19 +3226,8 @@
     <mergeCell ref="D26:K26"/>
     <mergeCell ref="D27:E27"/>
     <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="D49:K49"/>
-    <mergeCell ref="D50:E50"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C49:C50"/>
-    <mergeCell ref="C47:K48"/>
-    <mergeCell ref="J50:K50"/>
-    <mergeCell ref="A47:A55"/>
   </mergeCells>
-  <conditionalFormatting sqref="C4:E6">
+  <conditionalFormatting sqref="C4:E4">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
       <formula>4</formula>
     </cfRule>
@@ -3731,7 +3236,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E6" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Error de Ingreso - Nota debe estar entre 1,0 y 7,0" sqref="C4:E4" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>1</formula1>
       <formula2>7</formula2>
     </dataValidation>
@@ -3745,7 +3250,7 @@
           <x14:formula1>
             <xm:f>'RELEVANCIA-PUNTAJE'!$B$2:$E$2</xm:f>
           </x14:formula1>
-          <xm:sqref>C40:C42 C13:C19 C28:C30 C51:C53</xm:sqref>
+          <xm:sqref>C13:C19 C28:C30</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8614,7 +8119,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="71" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -8625,7 +8130,7 @@
       <c r="E1" s="9"/>
     </row>
     <row r="2" spans="1:5" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="63"/>
+      <c r="A2" s="72"/>
       <c r="B2" s="10" t="s">
         <v>5</v>
       </c>

--- a/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION FINAL FASE 2.xlsx
+++ b/Fase 2/Evidencias grupales/PLANILLA DE EVALUACION FINAL FASE 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\victo\OneDrive\Escritorio\Capstone\Capstone_DuocUc_2025\Fase 2\Evidencias grupales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B5855F-1421-41DA-AD0B-9487FDC92110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EA6A76-AE5E-46A0-84E3-41AB7752B72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="78">
   <si>
     <t>PUNTOS</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>Victor Gamboa Blanco</t>
+  </si>
+  <si>
+    <t>Victor Alejandro Gamboa Blanco</t>
   </si>
 </sst>
 </file>
@@ -968,10 +971,32 @@
     <xf numFmtId="0" fontId="12" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -980,28 +1005,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1622,7 +1625,7 @@
       <c r="D2" s="2">
         <v>0.25</v>
       </c>
-      <c r="E2" s="68">
+      <c r="E2" s="59">
         <v>1</v>
       </c>
     </row>
@@ -1636,13 +1639,15 @@
       <c r="D3" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="54"/>
+      <c r="E3" s="55"/>
     </row>
     <row r="4" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>1</v>
       </c>
-      <c r="B4" s="28"/>
+      <c r="B4" s="28" t="s">
+        <v>77</v>
+      </c>
       <c r="C4" s="5">
         <f>EVALUACION1!$C$21</f>
         <v>7</v>
@@ -1666,49 +1671,49 @@
       <c r="C6" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="18" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="69" t="s">
+      <c r="A11" s="62" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="15"/>
-      <c r="C11" s="61" t="s">
+      <c r="C11" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="D11" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="63"/>
-      <c r="F11" s="63"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="63"/>
-      <c r="I11" s="63"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="64"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="57"/>
     </row>
     <row r="12" spans="1:11" ht="14.4" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="62" t="s">
+      <c r="C12" s="55"/>
+      <c r="D12" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="62" t="s">
+      <c r="E12" s="57"/>
+      <c r="F12" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="64"/>
-      <c r="H12" s="65" t="s">
+      <c r="G12" s="57"/>
+      <c r="H12" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="64"/>
-      <c r="J12" s="62" t="s">
+      <c r="I12" s="57"/>
+      <c r="J12" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K12" s="64"/>
+      <c r="K12" s="57"/>
     </row>
     <row r="13" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="70"/>
+      <c r="A13" s="63"/>
       <c r="B13" s="31" t="str">
         <f>RUBRICA!A4</f>
         <v>1. Implementa una metodología que permite el logro de los objetivos propuestos, de acuerdo a los estándares de la disciplina.</v>
@@ -1750,7 +1755,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="36" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="70"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="31" t="str">
         <f>RUBRICA!A5</f>
         <v>2. Genera evidencias que dan cuenta del cumplimiento del Proyecto CAPSTONE, en relación a documentación, programación y almacenamiento de datos, de acuerdo a lo planificado por el equipo y que cumpla con estándares de desarrollo de la industria</v>
@@ -1792,7 +1797,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="14.4" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="70"/>
+      <c r="A15" s="63"/>
       <c r="B15" s="31" t="str">
         <f>RUBRICA!A7</f>
         <v>4. Relaciona el Proyecto APT con las competencias del perfil de egreso de su Plan de Estudio.</v>
@@ -1834,7 +1839,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="70"/>
+      <c r="A16" s="63"/>
       <c r="B16" s="31" t="str">
         <f>RUBRICA!A8</f>
         <v>5. Utiliza de manera precisa el lenguaje técnico en los entregables de acuerdo con lo requerido por la disciplina.</v>
@@ -1876,7 +1881,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="70"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="31" t="str">
         <f>RUBRICA!A9</f>
         <v xml:space="preserve">6. Utiliza correctamente las reglas de redacción, ortografía (literal, puntual, acentual) y las normas para citas y referencias. </v>
@@ -1918,7 +1923,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="24" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="70"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="31" t="str">
         <f>RUBRICA!A10</f>
         <v>7. Entrega la documentación y evidencias requerida por la asignatura de acuerdo a la estrucutra y nombres solicitados, guardando todas las evidencias de avances en Git</v>
@@ -1960,7 +1965,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="22.8" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="70"/>
+      <c r="A19" s="63"/>
       <c r="B19" s="31" t="str">
         <f>RUBRICA!A12</f>
         <v>9.-Generan evidencias claras dentro del repositorio  del aporte de cada uno de los integrantes del equipo que permitan identificar la equidad en el trabajo y la participación de cada estudiante.</v>
@@ -2002,7 +2007,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="67"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="30" t="s">
         <v>4</v>
       </c>
@@ -2032,7 +2037,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="54"/>
+      <c r="A21" s="55"/>
       <c r="B21" s="33" t="s">
         <v>13</v>
       </c>
@@ -2044,81 +2049,81 @@
     <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="66" t="s">
+      <c r="A24" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="64" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="55" t="s">
+      <c r="C24" s="65" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="56"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="57"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="66"/>
+      <c r="G24" s="66"/>
+      <c r="H24" s="66"/>
+      <c r="I24" s="66"/>
+      <c r="J24" s="66"/>
+      <c r="K24" s="67"/>
     </row>
     <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="67"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="60"/>
+      <c r="A25" s="54"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="70"/>
     </row>
     <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="67"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="61" t="s">
+      <c r="C26" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="62" t="s">
+      <c r="D26" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="64"/>
+      <c r="E26" s="61"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+      <c r="J26" s="61"/>
+      <c r="K26" s="57"/>
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="67"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="62" t="s">
+      <c r="C27" s="55"/>
+      <c r="D27" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E27" s="64"/>
-      <c r="F27" s="62" t="s">
+      <c r="E27" s="57"/>
+      <c r="F27" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="G27" s="64"/>
-      <c r="H27" s="65" t="s">
+      <c r="G27" s="57"/>
+      <c r="H27" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="64"/>
-      <c r="J27" s="62" t="s">
+      <c r="I27" s="57"/>
+      <c r="J27" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="K27" s="64"/>
+      <c r="K27" s="57"/>
     </row>
     <row r="28" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="67"/>
+      <c r="A28" s="54"/>
       <c r="B28" s="31" t="str">
         <f>RUBRICA!A6</f>
         <v>3. Relaciona el Proyecto APT con sus intereses profesionales. *</v>
@@ -2160,7 +2165,7 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="67"/>
+      <c r="A29" s="54"/>
       <c r="B29" s="31" t="str">
         <f>RUBRICA!A11</f>
         <v>8. Expone el tema utilizando un lenguaje técnico disciplinar al presentar la propuesta y responde evidenciando un manejo de la información. *</v>
@@ -2202,7 +2207,7 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="67"/>
+      <c r="A30" s="54"/>
       <c r="B30" s="31" t="str">
         <f>RUBRICA!A13</f>
         <v>10. Colaboración y trabajo en equipo *</v>
@@ -2244,7 +2249,7 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="67"/>
+      <c r="A31" s="54"/>
       <c r="B31" s="22" t="s">
         <v>14</v>
       </c>
@@ -2274,7 +2279,7 @@
       </c>
     </row>
     <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="54"/>
+      <c r="A32" s="55"/>
       <c r="B32" s="18" t="s">
         <v>13</v>
       </c>
@@ -2283,67 +2288,47 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="23"/>
       <c r="C33" s="24"/>
     </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="23"/>
       <c r="C34" s="24"/>
     </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="41" spans="1:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="42" spans="1:3" ht="14.4" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="66" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="67"/>
-    </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="67"/>
-    </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="67"/>
-    </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="67"/>
-    </row>
-    <row r="52" spans="1:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="67"/>
-    </row>
-    <row r="53" spans="1:3" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="67"/>
-    </row>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="67"/>
-    </row>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="54"/>
-    </row>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="40" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="2:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="42" spans="2:3" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="2:3" ht="25.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="53" spans="2:3" ht="14.4" x14ac:dyDescent="0.3"/>
+    <row r="54" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="23"/>
       <c r="C56" s="24"/>
     </row>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -3207,8 +3192,9 @@
     <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A47:A55"/>
+  <mergeCells count="17">
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="H27:I27"/>
     <mergeCell ref="J27:K27"/>
     <mergeCell ref="A24:A32"/>
@@ -3224,8 +3210,6 @@
     <mergeCell ref="C24:K25"/>
     <mergeCell ref="C26:C27"/>
     <mergeCell ref="D26:K26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
   </mergeCells>
   <conditionalFormatting sqref="C4:E4">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
